--- a/erp-server/erp-server-file/src/main/resources/excel/tms/firstMileCostAllocationExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/firstMileCostAllocationExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
   <si>
     <t>核算期间</t>
   </si>
@@ -139,6 +139,9 @@
     <t>分摊组织(￥)</t>
   </si>
   <si>
+    <t>备注</t>
+  </si>
+  <si>
     <t>创建时间</t>
   </si>
   <si>
@@ -254,6 +257,9 @@
   </si>
   <si>
     <t>{.orgName}</t>
+  </si>
+  <si>
+    <t>{.detailRemark}</t>
   </si>
   <si>
     <t>{.createTime}</t>
@@ -1227,7 +1233,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AM2"/>
+  <dimension ref="A1:AN2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="10.5" customWidth="1"/>
@@ -1254,7 +1260,7 @@
     <col min="30" max="35" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39">
+    <row r="1" spans="1:40">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1372,124 +1378,130 @@
       <c r="AM1" t="s">
         <v>38</v>
       </c>
+      <c r="AN1" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="2" spans="1:39">
+    <row r="2" spans="1:40">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Y2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Z2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AC2" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AD2" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AE2" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AF2" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AG2" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AH2" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AI2" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AJ2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AK2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AL2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AM2" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
